--- a/data/daily/2026-07/2026-07-24.xlsx
+++ b/data/daily/2026-07/2026-07-24.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -852,34 +852,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53,800원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13215071</t>
+          <t>https://gift.kakao.com/product/10848340</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260714110741_0c5ee4d65772453582e5a95846726854.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20241128105752_bb00bdfb255b4aad91bbff59ec2c2cfd.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -887,34 +887,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+쇼핑백 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62,000원</t>
+          <t>38,900원</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13255641</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260714111541_36039105cd90469f9c25fab78362086a.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260602111000_0f1c3a6d74c54029b701afe163b8f8ea.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -922,27 +922,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10848340</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20241128105752_bb00bdfb255b4aad91bbff59ec2c2cfd.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -992,34 +992,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)전자레인지 용기</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260602111000_0f1c3a6d74c54029b701afe163b8f8ea.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260707130836_45a6a961414d4844a5a8d6ec10e5c825.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
     </row>
@@ -1062,34 +1062,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>45,000원</t>
+          <t>53,800원</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/13215071</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260714110741_0c5ee4d65772453582e5a95846726854.jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1097,34 +1097,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260707130836_45a6a961414d4844a5a8d6ec10e5c825.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260701120356_f9d975374d374b858dd4262325030e55.jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1132,27 +1132,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
+          <t>[특허성분 고농축 숙취해소제] 알디콤A 선물세트 (5포입 x 3개 구성)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>25,000원</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/10590720</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260701120356_f9d975374d374b858dd4262325030e55.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260625180125_7d202367d1f745b5871f3fb6bc5bc550.png</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 (30일분)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1228,24 +1228,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1253,34 +1253,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 간케어 20포</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1303,19 +1303,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580891&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251015/nR3zXDtjAX4U4oB5HSV3591580891_00_00nR3zXDtjAX4U4oB5HSV3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1338,19 +1338,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651650&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/wjBYMQTwSs5Uxawy8JxO600651650_00_00wjBYMQTwSs5Uxawy8JxO.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>대웅제약 콘드로이친 30정 30일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000152&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/b7btdcjQN0UwyzjBmHvY600000152_00_00b7btdcjQN0UwyzjBmHvY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>동화 부채표 편안활 5포 5일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1408,19 +1408,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OgijyKEodb7qfhaHtw3p600000133_00_00OgijyKEodb7qfhaHtw3p.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1428,34 +1428,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 10정 10일분</t>
+          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000270&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651650&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/rjUOcdF4xff4PIy7VUYT600000270_00_01rjUOcdF4xff4PIy7VUYT.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/wjBYMQTwSs5Uxawy8JxO600651650_00_00wjBYMQTwSs5Uxawy8JxO.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1463,27 +1463,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
+          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651654&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/BJcWNz19ajlLYaMbOK0e600651654_00_00BJcWNz19ajlLYaMbOK0e.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/wJCESiflDyulw8oZ8pW1601618642_00_00wJCESiflDyulw8oZ8pW1.jpg</t>
         </is>
       </c>
     </row>
@@ -1498,27 +1498,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 초임계 알티지 오메가3 12캡슐 12일분</t>
+          <t>LG생활건강 이너뷰 루테인 지아잔틴 30캡슐</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953533&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/4kK0NmSBz1nQe0fBnnXY032306203_00_014kK0NmSBz1nQe0fBnnXY.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/lXFnthJvrHdOJJvI4JC2994953533_00_00lXFnthJvrHdOJJvI4JC2.jpg</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>자연관 바이탈 밀크씨슬＆비타민B 4병</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602146&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251211/MXX9ubQFCqeb0HoGBeRC613602146_00_01MXX9ubQFCqeb0HoGBeRC.jpg</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1654,34 +1654,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
+          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17,300원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245840&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024584012ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1689,27 +1689,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>올더베러 웰니스 구미 30일분 6종 택1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>9,500원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587409ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -1724,34 +1724,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>[1+1] 히말라야 숙취해소제 파티스마트 츄 [망고맛] 10P</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>히말라야</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29,300원</t>
+          <t>15,000원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229743&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846223ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022974324ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[7월 올영픽] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364582ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -1794,34 +1794,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 6종 택1</t>
+          <t>[7월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9,500원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587409ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563481ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1829,34 +1829,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39,000원</t>
+          <t>29,300원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846223ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1864,34 +1864,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[리뷰이벤트/10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 시그니처RN (10일분)</t>
+          <t>[독일1위] 도펠헤르츠 마칼디 칼슘 마그네슘 비타민D3 20포 (20일분)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>라이필</t>
+          <t>도펠헤르츠</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17,600원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259411&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000243633&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025941115ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024363315ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1899,34 +1899,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[1+1] 히말라야 숙취해소제 파티스마트 츄 [망고맛] 10P</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>히말라야</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15,000원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229743&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022974324ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1934,27 +1934,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입</t>
+          <t>[덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>39,000원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308648ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -2011,38 +2011,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -2051,23 +2051,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -2095,45 +2095,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2183,7 +2183,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2193,10 +2193,10 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -2205,7 +2205,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2215,10 +2215,10 @@
         <v>2.5</v>
       </c>
       <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
